--- a/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos huesos, articulaciones o musculares</t>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,53</t>
+          <t>0,42; 3,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,41</t>
+          <t>0,24; 2,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,1</t>
+          <t>0,33; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,05</t>
+          <t>0,3; 2,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,74</t>
+          <t>0,64; 3,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,55</t>
+          <t>0,66; 2,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,27</t>
+          <t>0,15; 1,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,47</t>
+          <t>0,14; 1,45</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,06</t>
+          <t>0,31; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,83</t>
+          <t>0,19; 1,73</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1118,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,14</t>
+          <t>0,17; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,22</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,67</t>
+          <t>0,4; 1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,23</t>
+          <t>0,28; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,97</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,92</t>
+          <t>0,27; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,94</t>
+          <t>0,32; 0,96</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4428</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>649; 5419</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2951</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4898</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>688; 6852</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4923</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3428</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>652; 6287</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4741</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5876</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1356; 7545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3746</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2682; 11248</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>647; 5384</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>617; 6277</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3095</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3347</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3408</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3752</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4566</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2333</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3920</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>636; 6564</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4264</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3931</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>781; 7166</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1184; 7671</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1355; 7909</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2847; 11565</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2018; 9021</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1281; 7323</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>584; 5077</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3760; 12663</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3337; 12194</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4688; 13915</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,54</t>
+          <t>0,42; 3,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,37</t>
+          <t>0,25; 2,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,22</t>
+          <t>0,33; 3,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,84</t>
+          <t>0,3; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,56</t>
+          <t>0,64; 3,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,76</t>
+          <t>0,67; 2,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,26</t>
+          <t>0,15; 1,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,45</t>
+          <t>0,16; 1,43</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,16</t>
+          <t>0,31; 3,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,73</t>
+          <t>0,15; 1,82</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,13</t>
+          <t>0,17; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,12</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,64</t>
+          <t>0,4; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,25</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,98</t>
+          <t>0,17; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,68</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,9</t>
+          <t>0,28; 0,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,84</t>
+          <t>0,23; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,96</t>
+          <t>0,29; 0,95</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4428</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3669</t>
+          <t>0; 3010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>649; 5419</t>
+          <t>645; 5456</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4898</t>
+          <t>0; 4418</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>688; 6852</t>
+          <t>728; 7326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4923</t>
+          <t>0; 4895</t>
         </is>
       </c>
     </row>
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>652; 6287</t>
+          <t>643; 6174</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4741</t>
+          <t>0; 4762</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>622; 5876</t>
+          <t>624; 6346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1356; 7545</t>
+          <t>1356; 7515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3746</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2682; 11248</t>
+          <t>2725; 10607</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>647; 5384</t>
+          <t>646; 6063</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>617; 6277</t>
+          <t>673; 6185</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3095</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3522</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3347</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3408</t>
+          <t>0; 4227</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3752</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 4769</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3920</t>
+          <t>0; 3958</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>636; 6564</t>
+          <t>637; 6381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4264</t>
+          <t>0; 2806</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3931</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>781; 7166</t>
+          <t>639; 7510</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1184; 7671</t>
+          <t>1183; 7365</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1355; 7909</t>
+          <t>1358; 8233</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2847; 11565</t>
+          <t>2826; 11751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2018; 9021</t>
+          <t>1378; 8198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1281; 7323</t>
+          <t>1256; 7159</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>584; 5077</t>
+          <t>587; 5421</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3760; 12663</t>
+          <t>3992; 12893</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3337; 12194</t>
+          <t>3368; 11708</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4688; 13915</t>
+          <t>4209; 13786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,42; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,56</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,53</t>
+          <t>0,24; 2,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,16</t>
+          <t>0,64; 3,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,54</t>
+          <t>0,33; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,32; 3,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,6</t>
+          <t>0,66; 2,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,42</t>
+          <t>0,15; 1,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,43</t>
+          <t>0,14; 1,47</t>
         </is>
       </c>
     </row>
@@ -850,27 +850,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,08</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,68</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 3,06</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,36</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,82</t>
+          <t>0,22; 1,83</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,08</t>
+          <t>0,19; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,17; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,96</t>
+          <t>0,19; 1,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,41; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,8</t>
+          <t>0,23; 0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,95</t>
+          <t>0,29; 0,94</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>735</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4455</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>648; 5405</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3385</t>
+          <t>0; 3635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>645; 5456</t>
+          <t>0; 3711</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3628</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 4380</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>728; 7326</t>
+          <t>687; 6988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4895</t>
+          <t>0; 4711</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3428</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2483</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1349</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2527</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3428</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>643; 6174</t>
+          <t>1364; 7935</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>0; 3116</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>624; 6346</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1356; 7515</t>
+          <t>652; 6044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3905</t>
+          <t>0; 4562</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>670; 6325</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2725; 10607</t>
+          <t>2694; 10380</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>646; 6063</t>
+          <t>647; 5426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673; 6185</t>
+          <t>622; 6351</t>
         </is>
       </c>
     </row>
@@ -1695,27 +1695,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>699</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 2466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 3045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>0; 3806</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4360</t>
+          <t>0; 4717</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4769</t>
+          <t>0; 4016</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1858,27 +1858,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2333</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>637; 6381</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,27 +1926,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>0; 3543</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>638; 6337</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2806</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>639; 7510</t>
+          <t>907; 7552</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6235</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1183; 7365</t>
+          <t>1381; 8886</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1358; 8233</t>
+          <t>1282; 7240</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2826; 11751</t>
+          <t>588; 5708</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1378; 8198</t>
+          <t>1167; 7780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1256; 7159</t>
+          <t>1360; 8640</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>587; 5421</t>
+          <t>2906; 11767</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3992; 12893</t>
+          <t>3899; 12960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3368; 11708</t>
+          <t>3401; 12177</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4209; 13786</t>
+          <t>4177; 13601</t>
         </is>
       </c>
     </row>
